--- a/VerveStacks_FIN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FIN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FIN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49AF54C6-53BE-4CCF-8EE0-3407108616CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E8692C9-2312-4F6E-A8A4-E7486FE82FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_FIN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FIN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FIN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E8692C9-2312-4F6E-A8A4-E7486FE82FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A90B019D-22A8-46F9-A90D-1069130B8219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_FIN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FIN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FIN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A90B019D-22A8-46F9-A90D-1069130B8219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C209636F-1D52-4D5B-B182-633E30C6DAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
